--- a/data_search/Cohort_Search.xlsx
+++ b/data_search/Cohort_Search.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\EHI_laterality\data_search\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953A817A-9AF0-4A40-AD6E-8998CBA9B9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1154019D-ECD0-4C30-A08A-302FDE7C017E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="10060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="papers" sheetId="1" r:id="rId1"/>
     <sheet name="NDA.nih.gov" sheetId="3" r:id="rId2"/>
     <sheet name="Closer discovery" sheetId="2" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">papers!$A$1:$GK$32</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="105">
   <si>
     <t>Title</t>
   </si>
@@ -46,9 +49,6 @@
     <t>Cohort name</t>
   </si>
   <si>
-    <t>DOI</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
@@ -65,6 +65,129 @@
   </si>
   <si>
     <t>Brisbane Adolescents Twin Sample (BATS)</t>
+  </si>
+  <si>
+    <t>Brisbane Adolescent Twin Study  Outline of study methods and research projects.pdf</t>
+  </si>
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>Valid</t>
+  </si>
+  <si>
+    <t>self report writing hand</t>
+  </si>
+  <si>
+    <t> Southampton Women's Survey</t>
+  </si>
+  <si>
+    <t>Some modified EHI, includes: hand to bat a ball, deal cards with, hammer a nail, strike a mtach, brush teeth, throw a ball, write. Some questions addressing mental health</t>
+  </si>
+  <si>
+    <t>https://discovery.closer.ac.uk/data/uk.lha/f4457c5f-1a2e-4216-a4eb-2096cae3350a</t>
+  </si>
+  <si>
+    <t> STRADL Clinic Questionnaire Dataset</t>
+  </si>
+  <si>
+    <t>self reported handedness including mixed</t>
+  </si>
+  <si>
+    <t> National Survey of Health and Development; 1989 Main Questionnaire Dataset</t>
+  </si>
+  <si>
+    <t>annete handedness inventory and mental health data</t>
+  </si>
+  <si>
+    <t>Prevalence and heritability of handedness in a Hong Kong Chinese twin and singleton sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mo Zheng, Catherine McBride, Connie Suk-Han Ho, Jonathan Ka-Chun Chan, Kwong Wai Choy &amp; Silvia Paracchini </t>
+  </si>
+  <si>
+    <t>Mental health data?</t>
+  </si>
+  <si>
+    <t>Adolescent Brain Cognitive Development (ABCD) study</t>
+  </si>
+  <si>
+    <t>HCP-D Mapping the Human Connectome During Typical Development (HCP-D) #2846</t>
+  </si>
+  <si>
+    <t>https://nda.nih.gov/edit_collection.html?id=2846</t>
+  </si>
+  <si>
+    <t>https://nda.nih.gov/study.html?id=1190</t>
+  </si>
+  <si>
+    <t>Avon Longitudinal Study of Parents and Children (ALSPAC) [1]</t>
+  </si>
+  <si>
+    <t>Collaborative Study on the Genetics of Alcoholism (COGA) [2]</t>
+  </si>
+  <si>
+    <t>Adriatic Island isolates, Croatia (CROATIA-Vis) [4]</t>
+  </si>
+  <si>
+    <t>Danish National Birth Cohort (DNBC) [7]</t>
+  </si>
+  <si>
+    <t>Estonian Genome Center, University of Tartu (EGCUT) [8, 9]</t>
+  </si>
+  <si>
+    <t>European Prospective Investigation into Cancer and Nutrition (EPIC) [10]</t>
+  </si>
+  <si>
+    <t>The Finnish Twin Cohort Study (FinnTwin)</t>
+  </si>
+  <si>
+    <t>Germany/Munich, part of SGENE-plus study (GER1) [6]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Health Professionals Follow-Up Study and Nurses’ Health Study HPFS/NHS</t>
+  </si>
+  <si>
+    <t>Cooperative Health Research in the Region of Augsburg (KORAF4) [20]</t>
+  </si>
+  <si>
+    <t>Korcula Island, Croatia (CROATIA-Korcula) [5]</t>
+  </si>
+  <si>
+    <t>Lothian Birth Cohort 1936 (LBC1936) [21, 22]</t>
+  </si>
+  <si>
+    <t>MICROS (MICROS) [23]</t>
+  </si>
+  <si>
+    <t>Northern Finish Birth Cohort 66 (NFBC66)</t>
+  </si>
+  <si>
+    <t>Norway/Thematic Organized Psychosis Research Study (NO) [6]</t>
+  </si>
+  <si>
+    <t>The Netherlands Twin Registry (NTR) [24, 25]</t>
+  </si>
+  <si>
+    <t>Queensland Institute of Medical Research (QIMR) [26]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systematic Treatment Enhansement Project for Bipolar Disorder (STEP) </t>
+  </si>
+  <si>
+    <t>Twins UK (TwinsUK) [28, 29]</t>
+  </si>
+  <si>
+    <t>TOP Cohort</t>
+  </si>
+  <si>
+    <t>Framingham Genetic Research Study (FRAMINGHAM)  [11-13]</t>
+  </si>
+  <si>
+    <t>Helsinki Birth Cohort Study (HBCS) [17, 18]</t>
+  </si>
+  <si>
+    <t>Iceland, deCODE Genetics (ICE) [19]</t>
   </si>
   <si>
     <r>
@@ -72,171 +195,279 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="Verdana"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>, </t>
     </r>
     <r>
       <rPr>
         <u/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="Verdana"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>Margie Wright</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="Verdana"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>, </t>
     </r>
     <r>
       <rPr>
         <u/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="Verdana"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>Nick Martin</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="Verdana"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>, </t>
     </r>
     <r>
       <rPr>
         <u/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="Verdana"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>Tim Bates</t>
     </r>
   </si>
   <si>
-    <t>Brisbane Adolescent Twin Study  Outline of study methods and research projects.pdf</t>
-  </si>
-  <si>
-    <t>Dataset</t>
-  </si>
-  <si>
-    <t>Valid</t>
-  </si>
-  <si>
-    <t>self report writing hand</t>
-  </si>
-  <si>
-    <t>preferred hand, it does have some mental health items</t>
-  </si>
-  <si>
-    <t> Southampton Women's Survey</t>
-  </si>
-  <si>
-    <t>Some modified EHI, includes: hand to bat a ball, deal cards with, hammer a nail, strike a mtach, brush teeth, throw a ball, write. Some questions addressing mental health</t>
-  </si>
-  <si>
-    <t>https://discovery.closer.ac.uk/data/uk.lha/f4457c5f-1a2e-4216-a4eb-2096cae3350a</t>
-  </si>
-  <si>
-    <t>ALSPAC Focus 10+ Clinic Dataset</t>
-  </si>
-  <si>
-    <t>Confusing random questions for handedness, extensive mental health report</t>
-  </si>
-  <si>
-    <t>ALSPAC Focus 11+ Clinic Dataset</t>
-  </si>
-  <si>
-    <t>ALSPAC Your Health Events and Feelings Questionnaire Dataset</t>
-  </si>
-  <si>
-    <t>left, mixed and right, extensive mental health data</t>
-  </si>
-  <si>
-    <t> STRADL Clinic Questionnaire Dataset</t>
-  </si>
-  <si>
-    <t>self reported handedness including mixed</t>
-  </si>
-  <si>
-    <t> National Survey of Health and Development; 1989 Main Questionnaire Dataset</t>
-  </si>
-  <si>
-    <t>annete handedness inventory and mental health data</t>
-  </si>
-  <si>
-    <t>Netherlands Twin Registry (NTR)</t>
-  </si>
-  <si>
-    <t>only self assessment handedness</t>
-  </si>
-  <si>
-    <t>Dorret Boomsma</t>
-  </si>
-  <si>
-    <t>Prevalence and heritability of handedness in a Hong Kong Chinese twin and singleton sample</t>
-  </si>
-  <si>
-    <t>hong knog twins study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mo Zheng, Catherine McBride, Connie Suk-Han Ho, Jonathan Ka-Chun Chan, Kwong Wai Choy &amp; Silvia Paracchini </t>
-  </si>
-  <si>
-    <t>Mental health data?</t>
-  </si>
-  <si>
-    <t>Adolescent Brain Cognitive Development (ABCD) study</t>
-  </si>
-  <si>
-    <t>HCP-D Mapping the Human Connectome During Typical Development (HCP-D) #2846</t>
-  </si>
-  <si>
-    <t>https://nda.nih.gov/edit_collection.html?id=2846</t>
-  </si>
-  <si>
-    <t>https://nda.nih.gov/study.html?id=1190</t>
+    <t xml:space="preserve">CoLaus (COLAUS) [3] </t>
+  </si>
+  <si>
+    <r>
+      <t>GenomEUtwin  (GENOMEUTWIN)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color rgb="FF00000A"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF00000A"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[14-16]</t>
+    </r>
+  </si>
+  <si>
+    <t>DOI /website</t>
+  </si>
+  <si>
+    <t>https://www.bristol.ac.uk/alspac/researchers/our-data/</t>
+  </si>
+  <si>
+    <t>he CoLaus study: a population-based study to investigate the genetic determinants of cardiovascular risk factors and metabolic syndrome. </t>
+  </si>
+  <si>
+    <t>Firmann et al</t>
+  </si>
+  <si>
+    <t>It contributed to latest GWAS, but no handedness info in their cookbook https://www.colaus-psycolaus.ch/fileadmin/colaus/phenotypes/codebook_description_instruments.pdf</t>
+  </si>
+  <si>
+    <t>https://www.colaus-psycolaus.ch/professionals/colaus</t>
+  </si>
+  <si>
+    <t>Data dictionary found</t>
+  </si>
+  <si>
+    <t>Yes, in Zip</t>
+  </si>
+  <si>
+    <t>Yes, in PDF</t>
+  </si>
+  <si>
+    <t>NIHR Bioresource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bioresource.nihr.ac.uk/centres-programmes/ibd-bioresource/gut-reaction-datasets-in-detail/ ; https://www.bioresource.nihr.ac.uk/media/4url1uzq/hlq_generic-health-and-lifestyle-questionnaire_20210902_1-6.pdf ; </t>
+  </si>
+  <si>
+    <t>Hand preference + mental health; you have to pay fees and application process looks long</t>
+  </si>
+  <si>
+    <t>No data publicly available, application process looks long</t>
+  </si>
+  <si>
+    <t>https://cogastudy.org/</t>
+  </si>
+  <si>
+    <t>Yes, in ZIP</t>
+  </si>
+  <si>
+    <t>Extensive amount of data relative to hand, so much data relative to mental health, dictionary checked, application looks easy enough</t>
+  </si>
+  <si>
+    <t>All of US</t>
+  </si>
+  <si>
+    <t>https://databrowser.researchallofus.org/ehr/conditions/hand</t>
+  </si>
+  <si>
+    <t>No handedness</t>
+  </si>
+  <si>
+    <t>Generation Scotland</t>
+  </si>
+  <si>
+    <t>https://genscot.ed.ac.uk/for-researchers/generation-scotland</t>
+  </si>
+  <si>
+    <t>No, but online search tool</t>
+  </si>
+  <si>
+    <t> Scottish Longitudinal Study Development Support Unit (SLS-DSU).</t>
+  </si>
+  <si>
+    <t>Yes, an excel</t>
+  </si>
+  <si>
+    <t>https://sls.lscs.ac.uk/variables/</t>
+  </si>
+  <si>
+    <t>Northern Ireland Longitudinal Study (NILS)</t>
+  </si>
+  <si>
+    <t>https://nisra.metadata.works/browser/dataset/9677/0</t>
+  </si>
+  <si>
+    <t>nothing about handedness</t>
+  </si>
+  <si>
+    <t>NHS England</t>
+  </si>
+  <si>
+    <t>https://digital.nhs.uk/data-and-information/data-tools-and-services/data-services/adult-social-care-data-hub?area=data-dictionary</t>
+  </si>
+  <si>
+    <t>National Survey of Health and Development</t>
+  </si>
+  <si>
+    <t>Yes, an excel, and also online https://www.datadictionary.nhs.uk/search.html?searchQuery=hand</t>
+  </si>
+  <si>
+    <t>nothing about handedness in excel; on website, Griffiths Eye and Hand Co-ordination Scale Score is retired, handedness code for joint replacement also considers ambidextrous</t>
+  </si>
+  <si>
+    <t>Yes, in Excel</t>
+  </si>
+  <si>
+    <t>Nothing</t>
+  </si>
+  <si>
+    <t>Yes, an Excel file</t>
+  </si>
+  <si>
+    <t>https://twinsuk.ac.uk/researchers/explore-our-data-and-samples/</t>
+  </si>
+  <si>
+    <t>Yes, also mental health</t>
+  </si>
+  <si>
+    <t>YES, from closer discovery you could download the data dictionary as pdf</t>
+  </si>
+  <si>
+    <t>handedness extensively assessed in 1989.</t>
+  </si>
+  <si>
+    <t>Not found</t>
+  </si>
+  <si>
+    <t>hong kong twins study</t>
+  </si>
+  <si>
+    <t>Yes, in PDF, but they are in Danish</t>
+  </si>
+  <si>
+    <t>Not available</t>
+  </si>
+  <si>
+    <t>The Rotterdam Study: objectives and design update</t>
+  </si>
+  <si>
+    <t>Albert Hofman 1,✉, Monique M B Breteler 1, Cornelia M van Duijn 1, Gabriel P Krestin 2, Huibert A Pols 1,3, Bruno H Ch Stricker 1,3, Henning Tiemeier 1, André G Uitterlinden 1,3, Johannes R Vingerling 1,4, Jacqueline C M Witteman</t>
+  </si>
+  <si>
+    <t>https://www.ergo-onderzoek.nl/research</t>
+  </si>
+  <si>
+    <r>
+      <t>Erasmus Rotterdam Gezondheid Onderzoek (ERGO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF474747"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>impossible, everything is in Dutch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cohort Profile: Cooperative Health Research in the Region of Augsburg (KORA) 1984–2024 </t>
+  </si>
+  <si>
+    <t>Birgit Linkohr , Margit Heier , Christian Gieger , Barbara Thorand , Harald Grallert , Rolf Holle , Stefan Karrasch , Wolfgang Koenig , Karl-Heinz Ladwig , Michael Laxy , Bettina Lorenz-Depiereux , Susanne Rospleszcz , Alexandra Schneider , Holger Schulz , Lars Schwettmann , Marie Standl , Melanie Waldenberger , Rui Wang-Sattler , Kathrin Wolf , Marco Dallavalle , Ina-Maria Rückert-Eheberg , Andrea Schneider , Reiner Leidl , Heinz-Erich Wichmann , Annette Peters</t>
+  </si>
+  <si>
+    <t>No: as said in the paper, you have to register in their website in order to access the data dictionary. Tried to register with the st andrews acc and not possible</t>
+  </si>
+  <si>
+    <t>(https://helmholtz-muenchen.managed-otrs.com/external)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Verdana"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -259,16 +490,86 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF00000A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="12"/>
+      <color rgb="FF00000A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FF767676"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF474747"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -276,23 +577,97 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -574,84 +949,739 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:GJ146"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="72.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="24.90625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="7.81640625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="6.453125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="15.7265625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="24.90625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="24.90625" style="4" customWidth="1"/>
+    <col min="8" max="192" width="9.1796875" style="11"/>
+    <col min="193" max="16384" width="9.1796875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+      <c r="A11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+      <c r="A13" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+      <c r="A15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:192" x14ac:dyDescent="0.35">
+      <c r="A17" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:192" ht="31" x14ac:dyDescent="0.35">
+      <c r="A18" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:192" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:192" ht="31" x14ac:dyDescent="0.2">
+      <c r="A20" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:192" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="22" spans="1:192" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C22" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="B4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="D22" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:192" ht="356.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:192" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="7"/>
+    </row>
+    <row r="25" spans="1:192" ht="33" x14ac:dyDescent="0.35">
+      <c r="A25" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="7"/>
+    </row>
+    <row r="26" spans="1:192" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="7" t="s">
         <v>33</v>
       </c>
-    </row>
+      <c r="B26" s="7"/>
+    </row>
+    <row r="27" spans="1:192" ht="31" x14ac:dyDescent="0.35">
+      <c r="A27" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="7"/>
+    </row>
+    <row r="28" spans="1:192" ht="62" x14ac:dyDescent="0.35">
+      <c r="A28" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="7"/>
+    </row>
+    <row r="29" spans="1:192" ht="31" x14ac:dyDescent="0.35">
+      <c r="A29" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="8"/>
+    </row>
+    <row r="30" spans="1:192" ht="124" x14ac:dyDescent="0.35">
+      <c r="A30" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:192" ht="31" x14ac:dyDescent="0.35">
+      <c r="A31" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:192" s="14" customFormat="1" ht="31" x14ac:dyDescent="0.35">
+      <c r="A32" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="11"/>
+      <c r="R32" s="11"/>
+      <c r="S32" s="11"/>
+      <c r="T32" s="11"/>
+      <c r="U32" s="11"/>
+      <c r="V32" s="11"/>
+      <c r="W32" s="11"/>
+      <c r="X32" s="11"/>
+      <c r="Y32" s="11"/>
+      <c r="Z32" s="11"/>
+      <c r="AA32" s="11"/>
+      <c r="AB32" s="11"/>
+      <c r="AC32" s="11"/>
+      <c r="AD32" s="11"/>
+      <c r="AE32" s="11"/>
+      <c r="AF32" s="11"/>
+      <c r="AG32" s="11"/>
+      <c r="AH32" s="11"/>
+      <c r="AI32" s="11"/>
+      <c r="AJ32" s="11"/>
+      <c r="AK32" s="11"/>
+      <c r="AL32" s="11"/>
+      <c r="AM32" s="11"/>
+      <c r="AN32" s="11"/>
+      <c r="AO32" s="11"/>
+      <c r="AP32" s="11"/>
+      <c r="AQ32" s="11"/>
+      <c r="AR32" s="11"/>
+      <c r="AS32" s="11"/>
+      <c r="AT32" s="11"/>
+      <c r="AU32" s="11"/>
+      <c r="AV32" s="11"/>
+      <c r="AW32" s="11"/>
+      <c r="AX32" s="11"/>
+      <c r="AY32" s="11"/>
+      <c r="AZ32" s="11"/>
+      <c r="BA32" s="11"/>
+      <c r="BB32" s="11"/>
+      <c r="BC32" s="11"/>
+      <c r="BD32" s="11"/>
+      <c r="BE32" s="11"/>
+      <c r="BF32" s="11"/>
+      <c r="BG32" s="11"/>
+      <c r="BH32" s="11"/>
+      <c r="BI32" s="11"/>
+      <c r="BJ32" s="11"/>
+      <c r="BK32" s="11"/>
+      <c r="BL32" s="11"/>
+      <c r="BM32" s="11"/>
+      <c r="BN32" s="11"/>
+      <c r="BO32" s="11"/>
+      <c r="BP32" s="11"/>
+      <c r="BQ32" s="11"/>
+      <c r="BR32" s="11"/>
+      <c r="BS32" s="11"/>
+      <c r="BT32" s="11"/>
+      <c r="BU32" s="11"/>
+      <c r="BV32" s="11"/>
+      <c r="BW32" s="11"/>
+      <c r="BX32" s="11"/>
+      <c r="BY32" s="11"/>
+      <c r="BZ32" s="11"/>
+      <c r="CA32" s="11"/>
+      <c r="CB32" s="11"/>
+      <c r="CC32" s="11"/>
+      <c r="CD32" s="11"/>
+      <c r="CE32" s="11"/>
+      <c r="CF32" s="11"/>
+      <c r="CG32" s="11"/>
+      <c r="CH32" s="11"/>
+      <c r="CI32" s="11"/>
+      <c r="CJ32" s="11"/>
+      <c r="CK32" s="11"/>
+      <c r="CL32" s="11"/>
+      <c r="CM32" s="11"/>
+      <c r="CN32" s="11"/>
+      <c r="CO32" s="11"/>
+      <c r="CP32" s="11"/>
+      <c r="CQ32" s="11"/>
+      <c r="CR32" s="11"/>
+      <c r="CS32" s="11"/>
+      <c r="CT32" s="11"/>
+      <c r="CU32" s="11"/>
+      <c r="CV32" s="11"/>
+      <c r="CW32" s="11"/>
+      <c r="CX32" s="11"/>
+      <c r="CY32" s="11"/>
+      <c r="CZ32" s="11"/>
+      <c r="DA32" s="11"/>
+      <c r="DB32" s="11"/>
+      <c r="DC32" s="11"/>
+      <c r="DD32" s="11"/>
+      <c r="DE32" s="11"/>
+      <c r="DF32" s="11"/>
+      <c r="DG32" s="11"/>
+      <c r="DH32" s="11"/>
+      <c r="DI32" s="11"/>
+      <c r="DJ32" s="11"/>
+      <c r="DK32" s="11"/>
+      <c r="DL32" s="11"/>
+      <c r="DM32" s="11"/>
+      <c r="DN32" s="11"/>
+      <c r="DO32" s="11"/>
+      <c r="DP32" s="11"/>
+      <c r="DQ32" s="11"/>
+      <c r="DR32" s="11"/>
+      <c r="DS32" s="11"/>
+      <c r="DT32" s="11"/>
+      <c r="DU32" s="11"/>
+      <c r="DV32" s="11"/>
+      <c r="DW32" s="11"/>
+      <c r="DX32" s="11"/>
+      <c r="DY32" s="11"/>
+      <c r="DZ32" s="11"/>
+      <c r="EA32" s="11"/>
+      <c r="EB32" s="11"/>
+      <c r="EC32" s="11"/>
+      <c r="ED32" s="11"/>
+      <c r="EE32" s="11"/>
+      <c r="EF32" s="11"/>
+      <c r="EG32" s="11"/>
+      <c r="EH32" s="11"/>
+      <c r="EI32" s="11"/>
+      <c r="EJ32" s="11"/>
+      <c r="EK32" s="11"/>
+      <c r="EL32" s="11"/>
+      <c r="EM32" s="11"/>
+      <c r="EN32" s="11"/>
+      <c r="EO32" s="11"/>
+      <c r="EP32" s="11"/>
+      <c r="EQ32" s="11"/>
+      <c r="ER32" s="11"/>
+      <c r="ES32" s="11"/>
+      <c r="ET32" s="11"/>
+      <c r="EU32" s="11"/>
+      <c r="EV32" s="11"/>
+      <c r="EW32" s="11"/>
+      <c r="EX32" s="11"/>
+      <c r="EY32" s="11"/>
+      <c r="EZ32" s="11"/>
+      <c r="FA32" s="11"/>
+      <c r="FB32" s="11"/>
+      <c r="FC32" s="11"/>
+      <c r="FD32" s="11"/>
+      <c r="FE32" s="11"/>
+      <c r="FF32" s="11"/>
+      <c r="FG32" s="11"/>
+      <c r="FH32" s="11"/>
+      <c r="FI32" s="11"/>
+      <c r="FJ32" s="11"/>
+      <c r="FK32" s="11"/>
+      <c r="FL32" s="11"/>
+      <c r="FM32" s="11"/>
+      <c r="FN32" s="11"/>
+      <c r="FO32" s="11"/>
+      <c r="FP32" s="11"/>
+      <c r="FQ32" s="11"/>
+      <c r="FR32" s="11"/>
+      <c r="FS32" s="11"/>
+      <c r="FT32" s="11"/>
+      <c r="FU32" s="11"/>
+      <c r="FV32" s="11"/>
+      <c r="FW32" s="11"/>
+      <c r="FX32" s="11"/>
+      <c r="FY32" s="11"/>
+      <c r="FZ32" s="11"/>
+      <c r="GA32" s="11"/>
+      <c r="GB32" s="11"/>
+      <c r="GC32" s="11"/>
+      <c r="GD32" s="11"/>
+      <c r="GE32" s="11"/>
+      <c r="GF32" s="11"/>
+      <c r="GG32" s="11"/>
+      <c r="GH32" s="11"/>
+      <c r="GI32" s="11"/>
+      <c r="GJ32" s="11"/>
+    </row>
+    <row r="33" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="7"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+    </row>
+    <row r="34" spans="1:7" s="11" customFormat="1" ht="31" x14ac:dyDescent="0.35">
+      <c r="A34" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35" spans="1:7" s="11" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="8"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+    </row>
+    <row r="36" spans="1:7" s="11" customFormat="1" ht="31" x14ac:dyDescent="0.35">
+      <c r="A36" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="7"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+    </row>
+    <row r="37" spans="1:7" s="11" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="7"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+    </row>
+    <row r="38" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="40" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="41" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="42" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="43" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="45" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="46" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="47" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="48" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="49" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="50" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="51" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="52" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="53" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="54" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="55" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="56" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="57" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="58" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="59" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="60" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="61" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="62" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="63" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="64" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="65" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="66" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="67" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="68" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="69" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="70" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="71" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="72" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="73" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="74" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="75" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="76" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="77" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="78" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="79" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="80" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="81" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="82" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="83" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="84" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="85" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="86" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="87" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="88" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="89" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="90" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="91" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="92" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="93" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="94" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="95" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="96" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="97" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="98" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="99" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="100" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="101" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="102" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="103" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="104" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="105" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="106" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="107" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="108" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="109" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="110" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="111" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="112" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="113" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="114" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="115" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="116" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="117" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="118" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="119" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="120" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="121" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="122" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="123" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="124" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="125" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="126" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="127" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="128" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="129" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="130" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="131" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="132" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="133" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="134" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="135" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="136" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="137" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="138" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="139" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="140" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="141" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="142" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="143" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="144" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="145" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="146" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
+  <autoFilter ref="A1:GK32" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:GJ37">
+      <sortCondition descending="1" ref="B1:B32"/>
+    </sortState>
+  </autoFilter>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" display="https://tweelingenregister.vu.nl/" xr:uid="{1E31E7B7-E2A9-4E68-BBAA-2F2E9E122951}"/>
-    <hyperlink ref="C4" r:id="rId2" display="https://research.vu.nl/en/persons/di-boomsma" xr:uid="{3A0FC621-C0B2-4EED-9AA4-9523BDDF39FA}"/>
+    <hyperlink ref="E30" r:id="rId1" display="https://helmholtz-muenchen.managed-otrs.com/external" xr:uid="{AD18AA64-16E2-4F03-87C8-7B6B3007B699}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -667,18 +1697,18 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>36</v>
+      <c r="A2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -701,70 +1731,54 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="B7" t="s">
         <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://discovery.closer.ac.uk/item/uk.mrcleu-uos.sws/03bdaf2d-f57a-487f-89f9-74150bfc3fad" xr:uid="{6E917224-2B6D-4E2D-A97B-3FEB08E15871}"/>
     <hyperlink ref="A4" r:id="rId2" display="https://discovery.closer.ac.uk/item/uk.lha/f8d235f7-49e5-4568-905e-7f1646e241eb" xr:uid="{B719850C-8022-4936-BE8F-6D5E3FE8D291}"/>
-    <hyperlink ref="A3" r:id="rId3" display="https://discovery.closer.ac.uk/item/uk.alspac/2d99470e-41ca-439d-9f66-ac7f6e818f79" xr:uid="{10D027F3-1363-4E8B-80A0-93F22C679AB1}"/>
-    <hyperlink ref="A7" r:id="rId4" display="https://discovery.closer.ac.uk/item/uk.genscot/92606ec1-d4e7-4826-abce-841ef81c30d2" xr:uid="{204769C0-2624-4457-8F98-728B81006DA5}"/>
-    <hyperlink ref="C4" r:id="rId5" xr:uid="{E544055E-8E9F-4D25-9121-CBD6815106E5}"/>
+    <hyperlink ref="A7" r:id="rId3" display="https://discovery.closer.ac.uk/item/uk.genscot/92606ec1-d4e7-4826-abce-841ef81c30d2" xr:uid="{204769C0-2624-4457-8F98-728B81006DA5}"/>
+    <hyperlink ref="C4" r:id="rId4" xr:uid="{E544055E-8E9F-4D25-9121-CBD6815106E5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_search/Cohort_Search.xlsx
+++ b/data_search/Cohort_Search.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\EHI_laterality\data_search\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1154019D-ECD0-4C30-A08A-302FDE7C017E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F1383A-D1F1-4767-B4AA-79A7EFC4C8BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -143,9 +143,6 @@
   </si>
   <si>
     <t>Germany/Munich, part of SGENE-plus study (GER1) [6]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Health Professionals Follow-Up Study and Nurses’ Health Study HPFS/NHS</t>
   </si>
   <si>
     <t>Cooperative Health Research in the Region of Augsburg (KORAF4) [20]</t>
@@ -290,9 +287,6 @@
     <t>DOI /website</t>
   </si>
   <si>
-    <t>https://www.bristol.ac.uk/alspac/researchers/our-data/</t>
-  </si>
-  <si>
     <t>he CoLaus study: a population-based study to investigate the genetic determinants of cardiovascular risk factors and metabolic syndrome. </t>
   </si>
   <si>
@@ -332,9 +326,6 @@
     <t>Yes, in ZIP</t>
   </si>
   <si>
-    <t>Extensive amount of data relative to hand, so much data relative to mental health, dictionary checked, application looks easy enough</t>
-  </si>
-  <si>
     <t>All of US</t>
   </si>
   <si>
@@ -351,9 +342,6 @@
   </si>
   <si>
     <t>No, but online search tool</t>
-  </si>
-  <si>
-    <t> Scottish Longitudinal Study Development Support Unit (SLS-DSU).</t>
   </si>
   <si>
     <t>Yes, an excel</t>
@@ -455,6 +443,18 @@
   </si>
   <si>
     <t>(https://helmholtz-muenchen.managed-otrs.com/external)</t>
+  </si>
+  <si>
+    <t>Health Professionals Follow-Up Study and Nurses’ Health Study HPFS/NHS</t>
+  </si>
+  <si>
+    <t>Scottish Longitudinal Study Development Support Unit (SLS-DSU).</t>
+  </si>
+  <si>
+    <t>https://www.bristol.ac.uk/alspac/researchers/our-data/  ;   https://www.bristol.ac.uk/alspac/researchers/our-data/genomics-data/</t>
+  </si>
+  <si>
+    <t>Extensive amount of data relative to hand, so much data relative to mental health, dictionary checked, application looks easy enough. Genomics and epigenomics</t>
   </si>
 </sst>
 </file>
@@ -623,7 +623,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -665,8 +665,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -967,7 +971,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>0</v>
@@ -976,7 +980,7 @@
         <v>5</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>2</v>
@@ -987,343 +991,328 @@
     </row>
     <row r="2" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>70</v>
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>94</v>
+        <v>57</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>60</v>
+      <c r="A6" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>85</v>
+        <v>64</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>82</v>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="124" x14ac:dyDescent="0.35">
+      <c r="A9" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="G9" s="15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="31" x14ac:dyDescent="0.35">
-      <c r="A11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>87</v>
+    </row>
+    <row r="11" spans="1:7" ht="31" x14ac:dyDescent="0.2">
+      <c r="A11" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>78</v>
+        <v>31</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="31" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>92</v>
+        <v>45</v>
+      </c>
+      <c r="B14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="17" spans="1:192" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+      <c r="B16" s="7"/>
+    </row>
+    <row r="17" spans="1:192" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:192" ht="31" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="B17" s="7"/>
+    </row>
+    <row r="18" spans="1:192" ht="62" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="19" spans="1:192" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" s="7"/>
+    </row>
+    <row r="19" spans="1:192" ht="31" x14ac:dyDescent="0.35">
+      <c r="A19" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="7"/>
+    </row>
+    <row r="20" spans="1:192" ht="356.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:192" ht="31" x14ac:dyDescent="0.35">
+      <c r="A21" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="8"/>
+    </row>
+    <row r="22" spans="1:192" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="7"/>
+    </row>
+    <row r="23" spans="1:192" ht="31" x14ac:dyDescent="0.35">
+      <c r="A23" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="7"/>
+    </row>
+    <row r="24" spans="1:192" x14ac:dyDescent="0.35">
+      <c r="A24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="7"/>
+    </row>
+    <row r="25" spans="1:192" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:192" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:192" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:192" ht="31" x14ac:dyDescent="0.35">
+      <c r="A28" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="7"/>
+    </row>
+    <row r="29" spans="1:192" ht="31" x14ac:dyDescent="0.35">
+      <c r="A29" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="1:192" ht="31" x14ac:dyDescent="0.2">
-      <c r="A20" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="21" spans="1:192" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:192" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:192" ht="356.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:192" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="7"/>
-    </row>
-    <row r="25" spans="1:192" ht="33" x14ac:dyDescent="0.35">
-      <c r="A25" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" s="7"/>
-    </row>
-    <row r="26" spans="1:192" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="7"/>
-    </row>
-    <row r="27" spans="1:192" ht="31" x14ac:dyDescent="0.35">
-      <c r="A27" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B27" s="7"/>
-    </row>
-    <row r="28" spans="1:192" ht="62" x14ac:dyDescent="0.35">
-      <c r="A28" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="7"/>
-    </row>
-    <row r="29" spans="1:192" ht="31" x14ac:dyDescent="0.35">
-      <c r="A29" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29" s="8"/>
-    </row>
-    <row r="30" spans="1:192" ht="124" x14ac:dyDescent="0.35">
-      <c r="A30" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="31" spans="1:192" ht="31" x14ac:dyDescent="0.35">
+      <c r="B29" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:192" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="8"/>
+      <c r="E30" s="19"/>
+    </row>
+    <row r="31" spans="1:192" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B31" s="7"/>
       <c r="F31" s="4"/>
     </row>
-    <row r="32" spans="1:192" s="14" customFormat="1" ht="31" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:192" s="14" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="7"/>
+        <v>102</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
+      <c r="E32" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
+      <c r="G32" s="4" t="s">
+        <v>75</v>
+      </c>
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
       <c r="J32" s="11"/>
@@ -1510,11 +1499,13 @@
       <c r="GI32" s="11"/>
       <c r="GJ32" s="11"/>
     </row>
-    <row r="33" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" s="11" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="7"/>
+        <v>42</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>88</v>
+      </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -1523,47 +1514,57 @@
     </row>
     <row r="34" spans="1:7" s="11" customFormat="1" ht="31" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="7"/>
+        <v>32</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>88</v>
+      </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
     </row>
-    <row r="35" spans="1:7" s="11" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="8" t="s">
+    <row r="35" spans="1:7" s="11" customFormat="1" ht="31" x14ac:dyDescent="0.35">
+      <c r="A35" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="8"/>
+      <c r="B35" s="7"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
     </row>
-    <row r="36" spans="1:7" s="11" customFormat="1" ht="31" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="7"/>
+        <v>44</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>88</v>
+      </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
     </row>
-    <row r="37" spans="1:7" s="11" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" s="11" customFormat="1" ht="31" x14ac:dyDescent="0.35">
       <c r="A37" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="7"/>
+        <v>43</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>83</v>
+      </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
+      <c r="E37" s="4" t="s">
+        <v>84</v>
+      </c>
       <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
+      <c r="G37" s="4" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="38" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="39" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.35"/>
@@ -1677,11 +1678,11 @@
   </sheetData>
   <autoFilter ref="A1:GK32" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:GJ37">
-      <sortCondition descending="1" ref="B1:B32"/>
+      <sortCondition ref="A1:A32"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="E30" r:id="rId1" display="https://helmholtz-muenchen.managed-otrs.com/external" xr:uid="{AD18AA64-16E2-4F03-87C8-7B6B3007B699}"/>
+    <hyperlink ref="E9" r:id="rId1" display="https://helmholtz-muenchen.managed-otrs.com/external" xr:uid="{AD18AA64-16E2-4F03-87C8-7B6B3007B699}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
